--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2018/Aircraft_Cumulative_Statistics_2018.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2018/Aircraft_Cumulative_Statistics_2018.xlsx
@@ -13,75 +13,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="45" uniqueCount="45">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A320NEO</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B737-9</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>A350-900</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B787-10</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -163,10 +193,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -186,40 +216,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -227,40 +257,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>46762652591</v>
+        <v>3409253174</v>
       </c>
       <c r="C2" s="0">
-        <v>55366048892</v>
+        <v>4337235526</v>
       </c>
       <c r="D2" s="0">
-        <v>668672</v>
+        <v>106540</v>
       </c>
       <c r="E2" s="0">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>259293</v>
+        <v>255520</v>
       </c>
       <c r="G2" s="0">
-        <v>3.1299999999999999</v>
+        <v>6.2800000000000002</v>
       </c>
       <c r="H2" s="0">
-        <v>10.31</v>
+        <v>9.1899999999999995</v>
       </c>
       <c r="I2" s="0">
-        <v>84.459999999999994</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="J2" s="0">
-        <v>1306</v>
+        <v>339</v>
       </c>
       <c r="K2" s="0">
-        <v>4183</v>
+        <v>669.38999999999999</v>
       </c>
       <c r="L2" s="0">
-        <v>25.640000000000001</v>
+        <v>13.390000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -268,40 +298,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>10148166202</v>
+        <v>7185308798</v>
       </c>
       <c r="C3" s="0">
-        <v>11980894416</v>
+        <v>9135728526</v>
       </c>
       <c r="D3" s="0">
-        <v>478661</v>
+        <v>96075</v>
       </c>
       <c r="E3" s="0">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>79523</v>
+        <v>516211</v>
       </c>
       <c r="G3" s="0">
-        <v>3.1800000000000002</v>
+        <v>5.4299999999999997</v>
       </c>
       <c r="H3" s="0">
-        <v>7.3399999999999999</v>
+        <v>7.8799999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>84.700000000000003</v>
+        <v>78.650000000000006</v>
       </c>
       <c r="J3" s="0">
-        <v>885</v>
+        <v>354</v>
       </c>
       <c r="K3" s="0">
-        <v>3849</v>
+        <v>1367.79</v>
       </c>
       <c r="L3" s="0">
-        <v>22.600000000000001</v>
+        <v>27.359999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="4">
@@ -309,40 +339,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>201248248741</v>
+        <v>3444621596</v>
       </c>
       <c r="C4" s="0">
-        <v>243468196062</v>
+        <v>4208190421</v>
       </c>
       <c r="D4" s="0">
-        <v>749894</v>
+        <v>168733</v>
       </c>
       <c r="E4" s="0">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="F4" s="0">
-        <v>1042751</v>
+        <v>96545</v>
       </c>
       <c r="G4" s="0">
-        <v>3.21</v>
+        <v>3.8700000000000001</v>
       </c>
       <c r="H4" s="0">
-        <v>10.390000000000001</v>
+        <v>8.0099999999999998</v>
       </c>
       <c r="I4" s="0">
-        <v>82.659999999999997</v>
+        <v>81.859999999999999</v>
       </c>
       <c r="J4" s="0">
-        <v>1267</v>
+        <v>625</v>
       </c>
       <c r="K4" s="0">
-        <v>5514</v>
+        <v>1419.6199999999999</v>
       </c>
       <c r="L4" s="0">
-        <v>30.809999999999999</v>
+        <v>20.370000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="5">
@@ -350,40 +380,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>185641711960</v>
+        <v>24081071896</v>
       </c>
       <c r="C5" s="0">
-        <v>215159749364</v>
+        <v>29873194371</v>
       </c>
       <c r="D5" s="0">
-        <v>835183</v>
+        <v>211761</v>
       </c>
       <c r="E5" s="0">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="F5" s="0">
-        <v>831930</v>
+        <v>613292</v>
       </c>
       <c r="G5" s="0">
-        <v>3.23</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="H5" s="0">
-        <v>10.65</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="I5" s="0">
-        <v>86.280000000000001</v>
+        <v>80.609999999999999</v>
       </c>
       <c r="J5" s="0">
-        <v>1342</v>
+        <v>643</v>
       </c>
       <c r="K5" s="0">
-        <v>5141</v>
+        <v>1311.3599999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>27.539999999999999</v>
+        <v>17.300000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="6">
@@ -391,40 +421,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>20875202333</v>
+        <v>9662877492</v>
       </c>
       <c r="C6" s="0">
-        <v>24443949064</v>
+        <v>12250536202</v>
       </c>
       <c r="D6" s="0">
-        <v>838845</v>
+        <v>146854</v>
       </c>
       <c r="E6" s="0">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="F6" s="0">
-        <v>122441</v>
+        <v>389614</v>
       </c>
       <c r="G6" s="0">
-        <v>4.2000000000000002</v>
+        <v>4.6699999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>11.69</v>
+        <v>7.7000000000000002</v>
       </c>
       <c r="I6" s="0">
-        <v>85.400000000000006</v>
+        <v>78.879999999999995</v>
       </c>
       <c r="J6" s="0">
-        <v>1052</v>
+        <v>460</v>
       </c>
       <c r="K6" s="0">
-        <v>4008</v>
+        <v>1251.6900000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>21.120000000000001</v>
+        <v>18.34</v>
       </c>
       <c r="M6" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="7">
@@ -432,40 +462,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>17190233073</v>
+        <v>6433325270</v>
       </c>
       <c r="C7" s="0">
-        <v>20147017075</v>
+        <v>7946799272</v>
       </c>
       <c r="D7" s="0">
-        <v>979913</v>
+        <v>273650</v>
       </c>
       <c r="E7" s="0">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="F7" s="0">
-        <v>89705</v>
+        <v>153979</v>
       </c>
       <c r="G7" s="0">
-        <v>4.3600000000000003</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="H7" s="0">
-        <v>9.9199999999999999</v>
+        <v>9.3499999999999996</v>
       </c>
       <c r="I7" s="0">
-        <v>85.319999999999993</v>
+        <v>80.950000000000003</v>
       </c>
       <c r="J7" s="0">
-        <v>901</v>
+        <v>517</v>
       </c>
       <c r="K7" s="0">
-        <v>6740</v>
+        <v>3579.9499999999998</v>
       </c>
       <c r="L7" s="0">
-        <v>29.079999999999998</v>
+        <v>35.880000000000003</v>
       </c>
       <c r="M7" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="8">
@@ -473,40 +503,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>50819592338</v>
+        <v>15592396718</v>
       </c>
       <c r="C8" s="0">
-        <v>60409181191</v>
+        <v>19678107162</v>
       </c>
       <c r="D8" s="0">
-        <v>670468</v>
+        <v>209475</v>
       </c>
       <c r="E8" s="0">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="F8" s="0">
-        <v>367443</v>
+        <v>502494</v>
       </c>
       <c r="G8" s="0">
-        <v>4.0800000000000001</v>
+        <v>5.3499999999999996</v>
       </c>
       <c r="H8" s="0">
-        <v>11.76</v>
+        <v>9.5</v>
       </c>
       <c r="I8" s="0">
-        <v>84.129999999999995</v>
+        <v>79.239999999999995</v>
       </c>
       <c r="J8" s="0">
-        <v>1093</v>
+        <v>514</v>
       </c>
       <c r="K8" s="0">
-        <v>3952</v>
+        <v>1081.24</v>
       </c>
       <c r="L8" s="0">
-        <v>26.739999999999998</v>
+        <v>14.19</v>
       </c>
       <c r="M8" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="9">
@@ -514,40 +544,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>133371040685</v>
+        <v>48142666321</v>
       </c>
       <c r="C9" s="0">
-        <v>159850173477</v>
+        <v>57239967978</v>
       </c>
       <c r="D9" s="0">
-        <v>604029</v>
+        <v>473410</v>
       </c>
       <c r="E9" s="0">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="F9" s="0">
-        <v>1375426</v>
+        <v>476877</v>
       </c>
       <c r="G9" s="0">
-        <v>5.2000000000000002</v>
+        <v>3.9399999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>10.619999999999999</v>
+        <v>9.7400000000000002</v>
       </c>
       <c r="I9" s="0">
-        <v>83.439999999999998</v>
+        <v>84.109999999999999</v>
       </c>
       <c r="J9" s="0">
-        <v>757</v>
+        <v>893</v>
       </c>
       <c r="K9" s="0">
-        <v>3732</v>
+        <v>3631.3499999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>24.420000000000002</v>
+        <v>27.079999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="10">
@@ -555,40 +585,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>30591799219</v>
+        <v>94571965159</v>
       </c>
       <c r="C10" s="0">
-        <v>36270040450</v>
+        <v>112018408909</v>
       </c>
       <c r="D10" s="0">
-        <v>835330</v>
+        <v>601506</v>
       </c>
       <c r="E10" s="0">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="F10" s="0">
-        <v>191168</v>
+        <v>676160</v>
       </c>
       <c r="G10" s="0">
-        <v>4.4000000000000004</v>
+        <v>3.6299999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>12.01</v>
+        <v>10</v>
       </c>
       <c r="I10" s="0">
-        <v>84.340000000000003</v>
+        <v>84.430000000000007</v>
       </c>
       <c r="J10" s="0">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="K10" s="0">
-        <v>3553</v>
+        <v>4382.2799999999997</v>
       </c>
       <c r="L10" s="0">
-        <v>19.440000000000001</v>
+        <v>27.539999999999999</v>
       </c>
       <c r="M10" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="11">
@@ -596,40 +626,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>4189014201</v>
+        <v>4703630513</v>
       </c>
       <c r="C11" s="0">
-        <v>5254202646</v>
+        <v>5555075442</v>
       </c>
       <c r="D11" s="0">
-        <v>569870</v>
+        <v>516751</v>
       </c>
       <c r="E11" s="0">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="F11" s="0">
-        <v>24181</v>
+        <v>28131</v>
       </c>
       <c r="G11" s="0">
         <v>2.6200000000000001</v>
       </c>
       <c r="H11" s="0">
-        <v>8.6199999999999992</v>
+        <v>7.3300000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>79.730000000000004</v>
+        <v>84.670000000000002</v>
       </c>
       <c r="J11" s="0">
-        <v>1317</v>
+        <v>1062</v>
       </c>
       <c r="K11" s="0">
-        <v>4160</v>
+        <v>6104.3400000000001</v>
       </c>
       <c r="L11" s="0">
-        <v>25.219999999999999</v>
+        <v>32.82</v>
       </c>
       <c r="M11" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="12">
@@ -637,40 +667,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>204781794621</v>
+        <v>98310670668</v>
       </c>
       <c r="C12" s="0">
-        <v>244575401125</v>
+        <v>114273576136</v>
       </c>
       <c r="D12" s="0">
-        <v>65535</v>
+        <v>852852</v>
       </c>
       <c r="E12" s="0">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F12" s="0">
-        <v>785007</v>
+        <v>476813</v>
       </c>
       <c r="G12" s="0">
-        <v>65535</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>65535</v>
+        <v>11.720000000000001</v>
       </c>
       <c r="I12" s="0">
-        <v>83.730000000000004</v>
+        <v>86.030000000000001</v>
       </c>
       <c r="J12" s="0">
-        <v>1584</v>
+        <v>1291</v>
       </c>
       <c r="K12" s="0">
-        <v>5549</v>
+        <v>4542.4499999999998</v>
       </c>
       <c r="L12" s="0">
-        <v>29.07</v>
+        <v>24.370000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="13">
@@ -678,40 +708,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>657197554</v>
+        <v>2602735471</v>
       </c>
       <c r="C13" s="0">
-        <v>797824350</v>
+        <v>3084348825</v>
       </c>
       <c r="D13" s="0">
-        <v>65535</v>
+        <v>679372</v>
       </c>
       <c r="E13" s="0">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="F13" s="0">
-        <v>46317</v>
+        <v>8683</v>
       </c>
       <c r="G13" s="0">
-        <v>65535</v>
+        <v>1.9099999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>65535</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="I13" s="0">
-        <v>82.370000000000005</v>
+        <v>84.390000000000001</v>
       </c>
       <c r="J13" s="0">
-        <v>345</v>
+        <v>1902</v>
       </c>
       <c r="K13" s="0">
-        <v>0</v>
+        <v>5112.3599999999997</v>
       </c>
       <c r="L13" s="0">
-        <v>0</v>
+        <v>27.379999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>0</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -719,40 +749,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>6851175353</v>
+        <v>9582458900</v>
       </c>
       <c r="C14" s="0">
-        <v>8634045026</v>
+        <v>11593478242</v>
       </c>
       <c r="D14" s="0">
-        <v>154510</v>
+        <v>289403</v>
       </c>
       <c r="E14" s="0">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="F14" s="0">
-        <v>255652</v>
+        <v>226638</v>
       </c>
       <c r="G14" s="0">
-        <v>4.5800000000000001</v>
+        <v>5.6600000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>7.9500000000000002</v>
+        <v>8.5999999999999996</v>
       </c>
       <c r="I14" s="0">
-        <v>79.349999999999994</v>
+        <v>82.650000000000006</v>
       </c>
       <c r="J14" s="0">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="K14" s="0">
-        <v>1120</v>
+        <v>4043.3899999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>16.030000000000001</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="M14" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="15">
@@ -760,40 +790,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5562182260</v>
+        <v>90758774196</v>
       </c>
       <c r="C15" s="0">
-        <v>7099454699</v>
+        <v>109753451689</v>
       </c>
       <c r="D15" s="0">
-        <v>80147</v>
+        <v>519986</v>
       </c>
       <c r="E15" s="0">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="F15" s="0">
-        <v>234243</v>
+        <v>1131703</v>
       </c>
       <c r="G15" s="0">
-        <v>2.6400000000000001</v>
+        <v>5.3600000000000003</v>
       </c>
       <c r="H15" s="0">
-        <v>4.46</v>
+        <v>10.25</v>
       </c>
       <c r="I15" s="0">
-        <v>78.349999999999994</v>
+        <v>82.689999999999998</v>
       </c>
       <c r="J15" s="0">
-        <v>476</v>
+        <v>687</v>
       </c>
       <c r="K15" s="0">
-        <v>1403</v>
+        <v>3923.5999999999999</v>
       </c>
       <c r="L15" s="0">
-        <v>22.43</v>
+        <v>27.789999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.076999999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -801,40 +831,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>2799588299</v>
+        <v>165054293416</v>
       </c>
       <c r="C16" s="0">
-        <v>3417316854</v>
+        <v>196220947250</v>
       </c>
       <c r="D16" s="0">
-        <v>173468</v>
+        <v>676577</v>
       </c>
       <c r="E16" s="0">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="F16" s="0">
-        <v>92970</v>
+        <v>1063783</v>
       </c>
       <c r="G16" s="0">
-        <v>4.7199999999999998</v>
+        <v>3.6699999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>8.2300000000000004</v>
+        <v>10.57</v>
       </c>
       <c r="I16" s="0">
-        <v>81.920000000000002</v>
+        <v>84.120000000000005</v>
       </c>
       <c r="J16" s="0">
-        <v>519</v>
+        <v>1114</v>
       </c>
       <c r="K16" s="0">
-        <v>1077</v>
+        <v>4037.96</v>
       </c>
       <c r="L16" s="0">
-        <v>15.210000000000001</v>
+        <v>24.41</v>
       </c>
       <c r="M16" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="17">
@@ -842,40 +872,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1055649396</v>
+        <v>4046864204</v>
       </c>
       <c r="C17" s="0">
-        <v>1288641392</v>
+        <v>4754244526</v>
       </c>
       <c r="D17" s="0">
-        <v>245924</v>
+        <v>454952</v>
       </c>
       <c r="E17" s="0">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="F17" s="0">
-        <v>26765</v>
+        <v>24726</v>
       </c>
       <c r="G17" s="0">
-        <v>5.1100000000000003</v>
+        <v>2.3700000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>9.7899999999999991</v>
+        <v>6.7599999999999998</v>
       </c>
       <c r="I17" s="0">
-        <v>81.920000000000002</v>
+        <v>85.120000000000005</v>
       </c>
       <c r="J17" s="0">
-        <v>633</v>
+        <v>1107</v>
       </c>
       <c r="K17" s="0">
-        <v>774</v>
+        <v>5521.0600000000004</v>
       </c>
       <c r="L17" s="0">
-        <v>10.17</v>
+        <v>31.800000000000001</v>
       </c>
       <c r="M17" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="18">
@@ -883,40 +913,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>8251766479</v>
+        <v>7534760154</v>
       </c>
       <c r="C18" s="0">
-        <v>10128037729</v>
+        <v>8810428605</v>
       </c>
       <c r="D18" s="0">
-        <v>225068</v>
+        <v>419345</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="F18" s="0">
-        <v>234365</v>
+        <v>46204</v>
       </c>
       <c r="G18" s="0">
-        <v>5.21</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H18" s="0">
-        <v>9.5099999999999998</v>
+        <v>6.1600000000000001</v>
       </c>
       <c r="I18" s="0">
-        <v>81.469999999999999</v>
+        <v>85.519999999999996</v>
       </c>
       <c r="J18" s="0">
-        <v>568</v>
+        <v>1067</v>
       </c>
       <c r="K18" s="0">
-        <v>1020</v>
+        <v>7552.21</v>
       </c>
       <c r="L18" s="0">
-        <v>13.42</v>
+        <v>42.259999999999998</v>
       </c>
       <c r="M18" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="19">
@@ -924,40 +954,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>977973736</v>
+        <v>75592980893</v>
       </c>
       <c r="C19" s="0">
-        <v>1258952194</v>
+        <v>87148108858</v>
       </c>
       <c r="D19" s="0">
-        <v>65535</v>
+        <v>879662</v>
       </c>
       <c r="E19" s="0">
-        <v>50</v>
+        <v>179</v>
       </c>
       <c r="F19" s="0">
-        <v>90937</v>
+        <v>375322</v>
       </c>
       <c r="G19" s="0">
-        <v>65535</v>
+        <v>3.79</v>
       </c>
       <c r="H19" s="0">
-        <v>65535</v>
+        <v>12.300000000000001</v>
       </c>
       <c r="I19" s="0">
-        <v>77.680000000000007</v>
+        <v>86.739999999999995</v>
       </c>
       <c r="J19" s="0">
-        <v>277</v>
+        <v>1297</v>
       </c>
       <c r="K19" s="0">
-        <v>0</v>
+        <v>3642.5700000000002</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>20.34</v>
       </c>
       <c r="M19" s="0">
-        <v>0</v>
+        <v>0.050999999999999997</v>
       </c>
     </row>
     <row r="20">
@@ -965,40 +995,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>5292012095</v>
+        <v>998927544</v>
       </c>
       <c r="C20" s="0">
-        <v>6907404356</v>
+        <v>1144280770</v>
       </c>
       <c r="D20" s="0">
-        <v>145388</v>
+        <v>657633</v>
       </c>
       <c r="E20" s="0">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="F20" s="0">
-        <v>270077</v>
+        <v>4913</v>
       </c>
       <c r="G20" s="0">
-        <v>5.6799999999999997</v>
+        <v>2.8199999999999998</v>
       </c>
       <c r="H20" s="0">
-        <v>8.5600000000000005</v>
+        <v>9.1099999999999994</v>
       </c>
       <c r="I20" s="0">
-        <v>76.609999999999999</v>
+        <v>87.299999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>386</v>
+        <v>1301</v>
       </c>
       <c r="K20" s="0">
-        <v>1355</v>
+        <v>3628.0999999999999</v>
       </c>
       <c r="L20" s="0">
-        <v>20.48</v>
+        <v>20.27</v>
       </c>
       <c r="M20" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -1006,40 +1036,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>11158068235</v>
+        <v>47537331635</v>
       </c>
       <c r="C21" s="0">
-        <v>14157584805</v>
+        <v>54552621363</v>
       </c>
       <c r="D21" s="0">
-        <v>205540</v>
+        <v>798838</v>
       </c>
       <c r="E21" s="0">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="F21" s="0">
-        <v>324089</v>
+        <v>178101</v>
       </c>
       <c r="G21" s="0">
-        <v>4.71</v>
+        <v>2.6099999999999999</v>
       </c>
       <c r="H21" s="0">
-        <v>9.3699999999999992</v>
+        <v>10.609999999999999</v>
       </c>
       <c r="I21" s="0">
-        <v>78.810000000000002</v>
+        <v>87.140000000000001</v>
       </c>
       <c r="J21" s="0">
-        <v>591</v>
+        <v>1717</v>
       </c>
       <c r="K21" s="0">
-        <v>1407</v>
+        <v>5065.0500000000002</v>
       </c>
       <c r="L21" s="0">
-        <v>19.030000000000001</v>
+        <v>28.32</v>
       </c>
       <c r="M21" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="22">
@@ -1047,40 +1077,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>20769916267</v>
+        <v>10877551232</v>
       </c>
       <c r="C22" s="0">
-        <v>25793730803</v>
+        <v>12560820189</v>
       </c>
       <c r="D22" s="0">
-        <v>173836</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0">
-        <v>62</v>
+        <v>227</v>
       </c>
       <c r="F22" s="0">
-        <v>798261</v>
+        <v>33688</v>
       </c>
       <c r="G22" s="0">
-        <v>5.3799999999999999</v>
+        <v>0</v>
       </c>
       <c r="H22" s="0">
-        <v>9.3800000000000008</v>
+        <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>80.519999999999996</v>
+        <v>86.599999999999994</v>
       </c>
       <c r="J22" s="0">
-        <v>492</v>
+        <v>1638</v>
       </c>
       <c r="K22" s="0">
-        <v>1309</v>
+        <v>5416.7799999999997</v>
       </c>
       <c r="L22" s="0">
-        <v>20.34</v>
+        <v>23.800000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1088,40 +1118,450 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>968994985638</v>
+        <v>41641443129</v>
       </c>
       <c r="C23" s="0">
-        <v>1156407845970</v>
+        <v>50016551380</v>
       </c>
       <c r="D23" s="0">
-        <v>65535</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0">
-        <v>132</v>
+        <v>217</v>
       </c>
       <c r="F23" s="0">
-        <v>7542544</v>
+        <v>66588</v>
       </c>
       <c r="G23" s="0">
-        <v>65535</v>
+        <v>0</v>
       </c>
       <c r="H23" s="0">
-        <v>65535</v>
+        <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>83.790000000000006</v>
+        <v>83.260000000000005</v>
       </c>
       <c r="J23" s="0">
-        <v>946</v>
+        <v>3482</v>
       </c>
       <c r="K23" s="0">
-        <v>4052</v>
+        <v>7027.1199999999999</v>
       </c>
       <c r="L23" s="0">
-        <v>26.57</v>
+        <v>32.57</v>
       </c>
       <c r="M23" s="0">
         <v>0.070000000000000007</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>15988719928</v>
+      </c>
+      <c r="C24" s="0">
+        <v>18980308189</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0">
+        <v>243</v>
+      </c>
+      <c r="F24" s="0">
+        <v>21011</v>
+      </c>
+      <c r="G24" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" s="0">
+        <v>0</v>
+      </c>
+      <c r="I24" s="0">
+        <v>84.239999999999995</v>
+      </c>
+      <c r="J24" s="0">
+        <v>3724</v>
+      </c>
+      <c r="K24" s="0">
+        <v>7117.2700000000004</v>
+      </c>
+      <c r="L24" s="0">
+        <v>29.34</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>23086790421</v>
+      </c>
+      <c r="C25" s="0">
+        <v>27863099120</v>
+      </c>
+      <c r="D25" s="0">
+        <v>1548810</v>
+      </c>
+      <c r="E25" s="0">
+        <v>260</v>
+      </c>
+      <c r="F25" s="0">
+        <v>31079</v>
+      </c>
+      <c r="G25" s="0">
+        <v>1.73</v>
+      </c>
+      <c r="H25" s="0">
+        <v>12.789999999999999</v>
+      </c>
+      <c r="I25" s="0">
+        <v>82.859999999999999</v>
+      </c>
+      <c r="J25" s="0">
+        <v>3474</v>
+      </c>
+      <c r="K25" s="0">
+        <v>8130.29</v>
+      </c>
+      <c r="L25" s="0">
+        <v>31.48</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>22962219029</v>
+      </c>
+      <c r="C26" s="0">
+        <v>27195121652</v>
+      </c>
+      <c r="D26" s="0">
+        <v>1909770</v>
+      </c>
+      <c r="E26" s="0">
+        <v>291</v>
+      </c>
+      <c r="F26" s="0">
+        <v>22930</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1.6100000000000001</v>
+      </c>
+      <c r="H26" s="0">
+        <v>13.66</v>
+      </c>
+      <c r="I26" s="0">
+        <v>84.439999999999998</v>
+      </c>
+      <c r="J26" s="0">
+        <v>4070</v>
+      </c>
+      <c r="K26" s="0">
+        <v>7935.8400000000001</v>
+      </c>
+      <c r="L26" s="0">
+        <v>27.239999999999998</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.057000000000000002</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>6602447079</v>
+      </c>
+      <c r="C27" s="0">
+        <v>7580779920</v>
+      </c>
+      <c r="D27" s="0">
+        <v>2159766</v>
+      </c>
+      <c r="E27" s="0">
+        <v>305</v>
+      </c>
+      <c r="F27" s="0">
+        <v>3919</v>
+      </c>
+      <c r="G27" s="0">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H27" s="0">
+        <v>13.869999999999999</v>
+      </c>
+      <c r="I27" s="0">
+        <v>87.090000000000003</v>
+      </c>
+      <c r="J27" s="0">
+        <v>6335</v>
+      </c>
+      <c r="K27" s="0">
+        <v>7957.6999999999998</v>
+      </c>
+      <c r="L27" s="0">
+        <v>26.059999999999999</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.050999999999999997</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>12937852301</v>
+      </c>
+      <c r="C28" s="0">
+        <v>15888310841</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1421137</v>
+      </c>
+      <c r="E28" s="0">
+        <v>223</v>
+      </c>
+      <c r="F28" s="0">
+        <v>15820</v>
+      </c>
+      <c r="G28" s="0">
+        <v>1.4199999999999999</v>
+      </c>
+      <c r="H28" s="0">
+        <v>12.83</v>
+      </c>
+      <c r="I28" s="0">
+        <v>81.430000000000007</v>
+      </c>
+      <c r="J28" s="0">
+        <v>4506</v>
+      </c>
+      <c r="K28" s="0">
+        <v>8030.8500000000004</v>
+      </c>
+      <c r="L28" s="0">
+        <v>36.020000000000003</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.071999999999999995</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>22896809589</v>
+      </c>
+      <c r="C29" s="0">
+        <v>28928489479</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1935016</v>
+      </c>
+      <c r="E29" s="0">
+        <v>265</v>
+      </c>
+      <c r="F29" s="0">
+        <v>18090</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.21</v>
+      </c>
+      <c r="H29" s="0">
+        <v>14.300000000000001</v>
+      </c>
+      <c r="I29" s="0">
+        <v>79.150000000000006</v>
+      </c>
+      <c r="J29" s="0">
+        <v>6056</v>
+      </c>
+      <c r="K29" s="0">
+        <v>8626.0400000000009</v>
+      </c>
+      <c r="L29" s="0">
+        <v>32.640000000000001</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>5663864</v>
+      </c>
+      <c r="C30" s="0">
+        <v>7539144</v>
+      </c>
+      <c r="D30" s="0">
+        <v>50261</v>
+      </c>
+      <c r="E30" s="0">
+        <v>318</v>
+      </c>
+      <c r="F30" s="0">
+        <v>13</v>
+      </c>
+      <c r="G30" s="0">
+        <v>0.089999999999999997</v>
+      </c>
+      <c r="H30" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="I30" s="0">
+        <v>75.129999999999995</v>
+      </c>
+      <c r="J30" s="0">
+        <v>1824</v>
+      </c>
+      <c r="K30" s="0">
+        <v>5208.2700000000004</v>
+      </c>
+      <c r="L30" s="0">
+        <v>16.379999999999999</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.037999999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>69993183659</v>
+      </c>
+      <c r="C31" s="0">
+        <v>85137298994</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1716824</v>
+      </c>
+      <c r="E31" s="0">
+        <v>290</v>
+      </c>
+      <c r="F31" s="0">
+        <v>67615</v>
+      </c>
+      <c r="G31" s="0">
+        <v>1.3600000000000001</v>
+      </c>
+      <c r="H31" s="0">
+        <v>12.25</v>
+      </c>
+      <c r="I31" s="0">
+        <v>82.209999999999994</v>
+      </c>
+      <c r="J31" s="0">
+        <v>4449</v>
+      </c>
+      <c r="K31" s="0">
+        <v>9805.8099999999995</v>
+      </c>
+      <c r="L31" s="0">
+        <v>34.579999999999998</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.070000000000000007</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>22755391389</v>
+      </c>
+      <c r="C32" s="0">
+        <v>28670796989</v>
+      </c>
+      <c r="D32" s="0">
+        <v>2183610</v>
+      </c>
+      <c r="E32" s="0">
+        <v>330</v>
+      </c>
+      <c r="F32" s="0">
+        <v>16082</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.22</v>
+      </c>
+      <c r="H32" s="0">
+        <v>13.050000000000001</v>
+      </c>
+      <c r="I32" s="0">
+        <v>79.370000000000005</v>
+      </c>
+      <c r="J32" s="0">
+        <v>5355</v>
+      </c>
+      <c r="K32" s="0">
+        <v>11037.6</v>
+      </c>
+      <c r="L32" s="0">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.066000000000000003</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>968994985638</v>
+      </c>
+      <c r="C33" s="0">
+        <v>1156407845970</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0">
+        <v>132</v>
+      </c>
+      <c r="F33" s="0">
+        <v>7542544</v>
+      </c>
+      <c r="G33" s="0">
+        <v>0</v>
+      </c>
+      <c r="H33" s="0">
+        <v>0</v>
+      </c>
+      <c r="I33" s="0">
+        <v>83.790000000000006</v>
+      </c>
+      <c r="J33" s="0">
+        <v>946</v>
+      </c>
+      <c r="K33" s="0">
+        <v>4051.6100000000001</v>
+      </c>
+      <c r="L33" s="0">
+        <v>26.57</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.067000000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2018/Aircraft_Cumulative_Statistics_2018.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2018/Aircraft_Cumulative_Statistics_2018.xlsx
@@ -13,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53" uniqueCount="53">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,6 +33,18 @@
     <t>E175</t>
   </si>
   <si>
+    <t>Q100</t>
+  </si>
+  <si>
+    <t>Q200</t>
+  </si>
+  <si>
+    <t>Q300</t>
+  </si>
+  <si>
+    <t>Q400</t>
+  </si>
+  <si>
     <t>CRJ-700</t>
   </si>
   <si>
@@ -54,7 +69,16 @@
     <t>A321NEO</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
     <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -193,7 +217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -216,40 +240,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
@@ -257,40 +281,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>3409253174</v>
+        <v>939401838</v>
       </c>
       <c r="C2" s="0">
-        <v>4337235526</v>
+        <v>1228168532</v>
       </c>
       <c r="D2" s="0">
-        <v>106540</v>
+        <v>34528</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F2" s="0">
-        <v>255520</v>
+        <v>78138</v>
       </c>
       <c r="G2" s="0">
-        <v>6.2800000000000002</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H2" s="0">
-        <v>9.1899999999999995</v>
+        <v>3.3100000000000001</v>
       </c>
       <c r="I2" s="0">
-        <v>78.599999999999994</v>
+        <v>76.489999999999995</v>
       </c>
       <c r="J2" s="0">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="K2" s="0">
-        <v>669.38999999999999</v>
+        <v>1368.1400000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>13.390000000000001</v>
+        <v>31.09</v>
       </c>
       <c r="M2" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.13100000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -298,40 +322,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>7185308798</v>
+        <v>3409253174</v>
       </c>
       <c r="C3" s="0">
-        <v>9135728526</v>
+        <v>4337235526</v>
       </c>
       <c r="D3" s="0">
-        <v>96075</v>
+        <v>106540</v>
       </c>
       <c r="E3" s="0">
         <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>516211</v>
+        <v>255520</v>
       </c>
       <c r="G3" s="0">
-        <v>5.4299999999999997</v>
+        <v>6.2800000000000002</v>
       </c>
       <c r="H3" s="0">
-        <v>7.8799999999999999</v>
+        <v>9.1899999999999995</v>
       </c>
       <c r="I3" s="0">
-        <v>78.650000000000006</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="J3" s="0">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="K3" s="0">
-        <v>1367.79</v>
+        <v>669.38999999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>27.359999999999999</v>
+        <v>13.390000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.112</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="4">
@@ -339,40 +363,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>3444621596</v>
+        <v>7185308798</v>
       </c>
       <c r="C4" s="0">
-        <v>4208190421</v>
+        <v>9135728526</v>
       </c>
       <c r="D4" s="0">
-        <v>168733</v>
+        <v>96075</v>
       </c>
       <c r="E4" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F4" s="0">
-        <v>96545</v>
+        <v>516211</v>
       </c>
       <c r="G4" s="0">
-        <v>3.8700000000000001</v>
+        <v>5.4299999999999997</v>
       </c>
       <c r="H4" s="0">
-        <v>8.0099999999999998</v>
+        <v>7.8799999999999999</v>
       </c>
       <c r="I4" s="0">
-        <v>81.859999999999999</v>
+        <v>78.650000000000006</v>
       </c>
       <c r="J4" s="0">
-        <v>625</v>
+        <v>354</v>
       </c>
       <c r="K4" s="0">
-        <v>1419.6199999999999</v>
+        <v>1367.79</v>
       </c>
       <c r="L4" s="0">
-        <v>20.370000000000001</v>
+        <v>27.359999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="5">
@@ -380,40 +404,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>24081071896</v>
+        <v>3444621596</v>
       </c>
       <c r="C5" s="0">
-        <v>29873194371</v>
+        <v>4208190421</v>
       </c>
       <c r="D5" s="0">
-        <v>211761</v>
+        <v>168733</v>
       </c>
       <c r="E5" s="0">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F5" s="0">
-        <v>613292</v>
+        <v>96545</v>
       </c>
       <c r="G5" s="0">
-        <v>4.3499999999999996</v>
+        <v>3.8700000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>8.9499999999999993</v>
+        <v>8.0099999999999998</v>
       </c>
       <c r="I5" s="0">
-        <v>80.609999999999999</v>
+        <v>81.859999999999999</v>
       </c>
       <c r="J5" s="0">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="K5" s="0">
-        <v>1311.3599999999999</v>
+        <v>1419.6199999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>17.300000000000001</v>
+        <v>20.370000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.055</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="6">
@@ -421,40 +445,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>9662877492</v>
+        <v>24081071896</v>
       </c>
       <c r="C6" s="0">
-        <v>12250536202</v>
+        <v>29873194371</v>
       </c>
       <c r="D6" s="0">
-        <v>146854</v>
+        <v>211761</v>
       </c>
       <c r="E6" s="0">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F6" s="0">
-        <v>389614</v>
+        <v>613292</v>
       </c>
       <c r="G6" s="0">
-        <v>4.6699999999999999</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="H6" s="0">
-        <v>7.7000000000000002</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="I6" s="0">
-        <v>78.879999999999995</v>
+        <v>80.609999999999999</v>
       </c>
       <c r="J6" s="0">
-        <v>460</v>
+        <v>643</v>
       </c>
       <c r="K6" s="0">
-        <v>1251.6900000000001</v>
+        <v>1311.3599999999999</v>
       </c>
       <c r="L6" s="0">
-        <v>18.34</v>
+        <v>17.300000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="7">
@@ -462,40 +486,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>6433325270</v>
+        <v>107996</v>
       </c>
       <c r="C7" s="0">
-        <v>7946799272</v>
+        <v>158434</v>
       </c>
       <c r="D7" s="0">
-        <v>273650</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="F7" s="0">
-        <v>153979</v>
+        <v>18</v>
       </c>
       <c r="G7" s="0">
-        <v>5.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="H7" s="0">
-        <v>9.3499999999999996</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0">
-        <v>80.950000000000003</v>
+        <v>68.159999999999997</v>
       </c>
       <c r="J7" s="0">
-        <v>517</v>
+        <v>238</v>
       </c>
       <c r="K7" s="0">
-        <v>3579.9499999999998</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0">
-        <v>35.880000000000003</v>
+        <v>0</v>
       </c>
       <c r="M7" s="0">
-        <v>0.122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -503,40 +527,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>15592396718</v>
+        <v>643712</v>
       </c>
       <c r="C8" s="0">
-        <v>19678107162</v>
+        <v>883560</v>
       </c>
       <c r="D8" s="0">
-        <v>209475</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F8" s="0">
-        <v>502494</v>
+        <v>126</v>
       </c>
       <c r="G8" s="0">
-        <v>5.3499999999999996</v>
+        <v>0</v>
       </c>
       <c r="H8" s="0">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I8" s="0">
-        <v>79.239999999999995</v>
+        <v>72.849999999999994</v>
       </c>
       <c r="J8" s="0">
-        <v>514</v>
+        <v>190</v>
       </c>
       <c r="K8" s="0">
-        <v>1081.24</v>
+        <v>0</v>
       </c>
       <c r="L8" s="0">
-        <v>14.19</v>
+        <v>0</v>
       </c>
       <c r="M8" s="0">
-        <v>0.049000000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -544,40 +568,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>48142666321</v>
+        <v>48172746</v>
       </c>
       <c r="C9" s="0">
-        <v>57239967978</v>
+        <v>65184288</v>
       </c>
       <c r="D9" s="0">
-        <v>473410</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="F9" s="0">
-        <v>476877</v>
+        <v>7834</v>
       </c>
       <c r="G9" s="0">
-        <v>3.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="H9" s="0">
-        <v>9.7400000000000002</v>
+        <v>0</v>
       </c>
       <c r="I9" s="0">
-        <v>84.109999999999999</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="J9" s="0">
-        <v>893</v>
+        <v>173</v>
       </c>
       <c r="K9" s="0">
-        <v>3631.3499999999999</v>
+        <v>0</v>
       </c>
       <c r="L9" s="0">
-        <v>27.079999999999998</v>
+        <v>0</v>
       </c>
       <c r="M9" s="0">
-        <v>0.074999999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -585,40 +609,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>94571965159</v>
+        <v>1537033319</v>
       </c>
       <c r="C10" s="0">
-        <v>112018408909</v>
+        <v>1983140580</v>
       </c>
       <c r="D10" s="0">
-        <v>601506</v>
+        <v>123483</v>
       </c>
       <c r="E10" s="0">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="F10" s="0">
-        <v>676160</v>
+        <v>96380</v>
       </c>
       <c r="G10" s="0">
-        <v>3.6299999999999999</v>
+        <v>6</v>
       </c>
       <c r="H10" s="0">
-        <v>10</v>
+        <v>7.2699999999999996</v>
       </c>
       <c r="I10" s="0">
-        <v>84.430000000000007</v>
+        <v>77.510000000000005</v>
       </c>
       <c r="J10" s="0">
-        <v>1041</v>
+        <v>271</v>
       </c>
       <c r="K10" s="0">
-        <v>4382.2799999999997</v>
+        <v>1785.0599999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>27.539999999999999</v>
+        <v>23.489999999999998</v>
       </c>
       <c r="M10" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="11">
@@ -626,40 +650,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>4703630513</v>
+        <v>9662877492</v>
       </c>
       <c r="C11" s="0">
-        <v>5555075442</v>
+        <v>12250536202</v>
       </c>
       <c r="D11" s="0">
-        <v>516751</v>
+        <v>146854</v>
       </c>
       <c r="E11" s="0">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="F11" s="0">
-        <v>28131</v>
+        <v>389614</v>
       </c>
       <c r="G11" s="0">
-        <v>2.6200000000000001</v>
+        <v>4.6699999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>7.3300000000000001</v>
+        <v>7.7000000000000002</v>
       </c>
       <c r="I11" s="0">
-        <v>84.670000000000002</v>
+        <v>78.879999999999995</v>
       </c>
       <c r="J11" s="0">
-        <v>1062</v>
+        <v>460</v>
       </c>
       <c r="K11" s="0">
-        <v>6104.3400000000001</v>
+        <v>1251.6900000000001</v>
       </c>
       <c r="L11" s="0">
-        <v>32.82</v>
+        <v>18.34</v>
       </c>
       <c r="M11" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="12">
@@ -667,40 +691,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>98310670668</v>
+        <v>6433325270</v>
       </c>
       <c r="C12" s="0">
-        <v>114273576136</v>
+        <v>7946799272</v>
       </c>
       <c r="D12" s="0">
-        <v>852852</v>
+        <v>273650</v>
       </c>
       <c r="E12" s="0">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="F12" s="0">
-        <v>476813</v>
+        <v>153979</v>
       </c>
       <c r="G12" s="0">
-        <v>3.5600000000000001</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="H12" s="0">
-        <v>11.720000000000001</v>
+        <v>9.3499999999999996</v>
       </c>
       <c r="I12" s="0">
-        <v>86.030000000000001</v>
+        <v>80.950000000000003</v>
       </c>
       <c r="J12" s="0">
-        <v>1291</v>
+        <v>517</v>
       </c>
       <c r="K12" s="0">
-        <v>4542.4499999999998</v>
+        <v>3579.9499999999998</v>
       </c>
       <c r="L12" s="0">
-        <v>24.370000000000001</v>
+        <v>35.880000000000003</v>
       </c>
       <c r="M12" s="0">
-        <v>0.062</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="13">
@@ -708,40 +732,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>2602735471</v>
+        <v>15592396718</v>
       </c>
       <c r="C13" s="0">
-        <v>3084348825</v>
+        <v>19678107162</v>
       </c>
       <c r="D13" s="0">
-        <v>679372</v>
+        <v>209475</v>
       </c>
       <c r="E13" s="0">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="F13" s="0">
-        <v>8683</v>
+        <v>502494</v>
       </c>
       <c r="G13" s="0">
-        <v>1.9099999999999999</v>
+        <v>5.3499999999999996</v>
       </c>
       <c r="H13" s="0">
-        <v>8.6199999999999992</v>
+        <v>9.5</v>
       </c>
       <c r="I13" s="0">
-        <v>84.390000000000001</v>
+        <v>79.239999999999995</v>
       </c>
       <c r="J13" s="0">
-        <v>1902</v>
+        <v>514</v>
       </c>
       <c r="K13" s="0">
-        <v>5112.3599999999997</v>
+        <v>1081.24</v>
       </c>
       <c r="L13" s="0">
-        <v>27.379999999999999</v>
+        <v>14.19</v>
       </c>
       <c r="M13" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -749,40 +773,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>9582458900</v>
+        <v>48142666321</v>
       </c>
       <c r="C14" s="0">
-        <v>11593478242</v>
+        <v>57239967978</v>
       </c>
       <c r="D14" s="0">
-        <v>289403</v>
+        <v>473410</v>
       </c>
       <c r="E14" s="0">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="F14" s="0">
-        <v>226638</v>
+        <v>476877</v>
       </c>
       <c r="G14" s="0">
-        <v>5.6600000000000001</v>
+        <v>3.9399999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>8.5999999999999996</v>
+        <v>9.7400000000000002</v>
       </c>
       <c r="I14" s="0">
-        <v>82.650000000000006</v>
+        <v>84.109999999999999</v>
       </c>
       <c r="J14" s="0">
-        <v>459</v>
+        <v>893</v>
       </c>
       <c r="K14" s="0">
-        <v>4043.3899999999999</v>
+        <v>3631.3499999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>35.950000000000003</v>
+        <v>27.079999999999998</v>
       </c>
       <c r="M14" s="0">
-        <v>0.12</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="15">
@@ -790,40 +814,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>90758774196</v>
+        <v>94571965159</v>
       </c>
       <c r="C15" s="0">
-        <v>109753451689</v>
+        <v>112018408909</v>
       </c>
       <c r="D15" s="0">
-        <v>519986</v>
+        <v>601506</v>
       </c>
       <c r="E15" s="0">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F15" s="0">
-        <v>1131703</v>
+        <v>676160</v>
       </c>
       <c r="G15" s="0">
-        <v>5.3600000000000003</v>
+        <v>3.6299999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="I15" s="0">
-        <v>82.689999999999998</v>
+        <v>84.430000000000007</v>
       </c>
       <c r="J15" s="0">
-        <v>687</v>
+        <v>1041</v>
       </c>
       <c r="K15" s="0">
-        <v>3923.5999999999999</v>
+        <v>4382.2799999999997</v>
       </c>
       <c r="L15" s="0">
-        <v>27.789999999999999</v>
+        <v>27.539999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.076999999999999999</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="16">
@@ -831,40 +855,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>165054293416</v>
+        <v>4703630513</v>
       </c>
       <c r="C16" s="0">
-        <v>196220947250</v>
+        <v>5555075442</v>
       </c>
       <c r="D16" s="0">
-        <v>676577</v>
+        <v>516751</v>
       </c>
       <c r="E16" s="0">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F16" s="0">
-        <v>1063783</v>
+        <v>28131</v>
       </c>
       <c r="G16" s="0">
-        <v>3.6699999999999999</v>
+        <v>2.6200000000000001</v>
       </c>
       <c r="H16" s="0">
-        <v>10.57</v>
+        <v>7.3300000000000001</v>
       </c>
       <c r="I16" s="0">
-        <v>84.120000000000005</v>
+        <v>84.670000000000002</v>
       </c>
       <c r="J16" s="0">
-        <v>1114</v>
+        <v>1062</v>
       </c>
       <c r="K16" s="0">
-        <v>4037.96</v>
+        <v>6104.3400000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>24.41</v>
+        <v>32.82</v>
       </c>
       <c r="M16" s="0">
-        <v>0.063</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="17">
@@ -872,40 +896,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>4046864204</v>
+        <v>98310670668</v>
       </c>
       <c r="C17" s="0">
-        <v>4754244526</v>
+        <v>114273576136</v>
       </c>
       <c r="D17" s="0">
-        <v>454952</v>
+        <v>852852</v>
       </c>
       <c r="E17" s="0">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="F17" s="0">
-        <v>24726</v>
+        <v>476813</v>
       </c>
       <c r="G17" s="0">
-        <v>2.3700000000000001</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>6.7599999999999998</v>
+        <v>11.720000000000001</v>
       </c>
       <c r="I17" s="0">
-        <v>85.120000000000005</v>
+        <v>86.030000000000001</v>
       </c>
       <c r="J17" s="0">
-        <v>1107</v>
+        <v>1291</v>
       </c>
       <c r="K17" s="0">
-        <v>5521.0600000000004</v>
+        <v>4542.4499999999998</v>
       </c>
       <c r="L17" s="0">
-        <v>31.800000000000001</v>
+        <v>24.370000000000001</v>
       </c>
       <c r="M17" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="18">
@@ -913,40 +937,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>7534760154</v>
+        <v>2602735471</v>
       </c>
       <c r="C18" s="0">
-        <v>8810428605</v>
+        <v>3084348825</v>
       </c>
       <c r="D18" s="0">
-        <v>419345</v>
+        <v>679372</v>
       </c>
       <c r="E18" s="0">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F18" s="0">
-        <v>46204</v>
+        <v>8683</v>
       </c>
       <c r="G18" s="0">
-        <v>2.2000000000000002</v>
+        <v>1.9099999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>6.1600000000000001</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="I18" s="0">
-        <v>85.519999999999996</v>
+        <v>84.390000000000001</v>
       </c>
       <c r="J18" s="0">
-        <v>1067</v>
+        <v>1902</v>
       </c>
       <c r="K18" s="0">
-        <v>7552.21</v>
+        <v>5112.3599999999997</v>
       </c>
       <c r="L18" s="0">
-        <v>42.259999999999998</v>
+        <v>27.379999999999999</v>
       </c>
       <c r="M18" s="0">
-        <v>0.111</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -954,40 +978,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>75592980893</v>
+        <v>18041237137</v>
       </c>
       <c r="C19" s="0">
-        <v>87148108858</v>
+        <v>21429279192</v>
       </c>
       <c r="D19" s="0">
-        <v>879662</v>
+        <v>372230</v>
       </c>
       <c r="E19" s="0">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="F19" s="0">
-        <v>375322</v>
+        <v>264693</v>
       </c>
       <c r="G19" s="0">
-        <v>3.79</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H19" s="0">
-        <v>12.300000000000001</v>
+        <v>7.9400000000000004</v>
       </c>
       <c r="I19" s="0">
-        <v>86.739999999999995</v>
+        <v>84.189999999999998</v>
       </c>
       <c r="J19" s="0">
-        <v>1297</v>
+        <v>545</v>
       </c>
       <c r="K19" s="0">
-        <v>3642.5700000000002</v>
+        <v>4428.8800000000001</v>
       </c>
       <c r="L19" s="0">
-        <v>20.34</v>
+        <v>29.859999999999999</v>
       </c>
       <c r="M19" s="0">
-        <v>0.050999999999999997</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="20">
@@ -995,40 +1019,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>998927544</v>
+        <v>7164767306</v>
       </c>
       <c r="C20" s="0">
-        <v>1144280770</v>
+        <v>8487567266</v>
       </c>
       <c r="D20" s="0">
-        <v>657633</v>
+        <v>428017</v>
       </c>
       <c r="E20" s="0">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="F20" s="0">
-        <v>4913</v>
+        <v>76732</v>
       </c>
       <c r="G20" s="0">
-        <v>2.8199999999999998</v>
+        <v>3.8700000000000001</v>
       </c>
       <c r="H20" s="0">
-        <v>9.1099999999999994</v>
+        <v>7.8499999999999996</v>
       </c>
       <c r="I20" s="0">
-        <v>87.299999999999997</v>
+        <v>84.409999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>1301</v>
+        <v>700</v>
       </c>
       <c r="K20" s="0">
-        <v>3628.0999999999999</v>
+        <v>4412.0799999999999</v>
       </c>
       <c r="L20" s="0">
-        <v>20.27</v>
+        <v>27.93</v>
       </c>
       <c r="M20" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -1036,40 +1060,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>47537331635</v>
+        <v>9582458900</v>
       </c>
       <c r="C21" s="0">
-        <v>54552621363</v>
+        <v>11593478242</v>
       </c>
       <c r="D21" s="0">
-        <v>798838</v>
+        <v>289403</v>
       </c>
       <c r="E21" s="0">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="F21" s="0">
-        <v>178101</v>
+        <v>226638</v>
       </c>
       <c r="G21" s="0">
-        <v>2.6099999999999999</v>
+        <v>5.6600000000000001</v>
       </c>
       <c r="H21" s="0">
-        <v>10.609999999999999</v>
+        <v>8.5999999999999996</v>
       </c>
       <c r="I21" s="0">
-        <v>87.140000000000001</v>
+        <v>82.650000000000006</v>
       </c>
       <c r="J21" s="0">
-        <v>1717</v>
+        <v>459</v>
       </c>
       <c r="K21" s="0">
-        <v>5065.0500000000002</v>
+        <v>4043.3899999999999</v>
       </c>
       <c r="L21" s="0">
-        <v>28.32</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="M21" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="22">
@@ -1077,40 +1101,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>10877551232</v>
+        <v>78103877</v>
       </c>
       <c r="C22" s="0">
-        <v>12560820189</v>
+        <v>145117104</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>2073101</v>
       </c>
       <c r="E22" s="0">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="F22" s="0">
-        <v>33688</v>
+        <v>1530</v>
       </c>
       <c r="G22" s="0">
-        <v>0</v>
+        <v>21.859999999999999</v>
       </c>
       <c r="H22" s="0">
-        <v>0</v>
+        <v>39.560000000000002</v>
       </c>
       <c r="I22" s="0">
-        <v>86.599999999999994</v>
+        <v>53.82</v>
       </c>
       <c r="J22" s="0">
-        <v>1638</v>
+        <v>565</v>
       </c>
       <c r="K22" s="0">
-        <v>5416.7799999999997</v>
+        <v>714.95000000000005</v>
       </c>
       <c r="L22" s="0">
-        <v>23.800000000000001</v>
+        <v>4.2599999999999998</v>
       </c>
       <c r="M22" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="23">
@@ -1118,40 +1142,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>41641443129</v>
+        <v>90758774196</v>
       </c>
       <c r="C23" s="0">
-        <v>50016551380</v>
+        <v>109753451689</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>519986</v>
       </c>
       <c r="E23" s="0">
-        <v>217</v>
+        <v>142</v>
       </c>
       <c r="F23" s="0">
-        <v>66588</v>
+        <v>1131703</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>5.3600000000000003</v>
       </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="I23" s="0">
-        <v>83.260000000000005</v>
+        <v>82.689999999999998</v>
       </c>
       <c r="J23" s="0">
-        <v>3482</v>
+        <v>687</v>
       </c>
       <c r="K23" s="0">
-        <v>7027.1199999999999</v>
+        <v>3923.5999999999999</v>
       </c>
       <c r="L23" s="0">
-        <v>32.57</v>
+        <v>27.789999999999999</v>
       </c>
       <c r="M23" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.076999999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1159,40 +1183,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>15988719928</v>
+        <v>165054293416</v>
       </c>
       <c r="C24" s="0">
-        <v>18980308189</v>
+        <v>196220947250</v>
       </c>
       <c r="D24" s="0">
-        <v>0</v>
+        <v>676577</v>
       </c>
       <c r="E24" s="0">
-        <v>243</v>
+        <v>166</v>
       </c>
       <c r="F24" s="0">
-        <v>21011</v>
+        <v>1063783</v>
       </c>
       <c r="G24" s="0">
-        <v>0</v>
+        <v>3.6699999999999999</v>
       </c>
       <c r="H24" s="0">
-        <v>0</v>
+        <v>10.57</v>
       </c>
       <c r="I24" s="0">
-        <v>84.239999999999995</v>
+        <v>84.120000000000005</v>
       </c>
       <c r="J24" s="0">
-        <v>3724</v>
+        <v>1114</v>
       </c>
       <c r="K24" s="0">
-        <v>7117.2700000000004</v>
+        <v>4037.96</v>
       </c>
       <c r="L24" s="0">
-        <v>29.34</v>
+        <v>24.41</v>
       </c>
       <c r="M24" s="0">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="25">
@@ -1200,40 +1224,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>23086790421</v>
+        <v>4046864204</v>
       </c>
       <c r="C25" s="0">
-        <v>27863099120</v>
+        <v>4754244526</v>
       </c>
       <c r="D25" s="0">
-        <v>1548810</v>
+        <v>454952</v>
       </c>
       <c r="E25" s="0">
-        <v>260</v>
+        <v>174</v>
       </c>
       <c r="F25" s="0">
-        <v>31079</v>
+        <v>24726</v>
       </c>
       <c r="G25" s="0">
-        <v>1.73</v>
+        <v>2.3700000000000001</v>
       </c>
       <c r="H25" s="0">
-        <v>12.789999999999999</v>
+        <v>6.7599999999999998</v>
       </c>
       <c r="I25" s="0">
-        <v>82.859999999999999</v>
+        <v>85.120000000000005</v>
       </c>
       <c r="J25" s="0">
-        <v>3474</v>
+        <v>1107</v>
       </c>
       <c r="K25" s="0">
-        <v>8130.29</v>
+        <v>5521.0600000000004</v>
       </c>
       <c r="L25" s="0">
-        <v>31.48</v>
+        <v>31.800000000000001</v>
       </c>
       <c r="M25" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="26">
@@ -1241,40 +1265,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>22962219029</v>
+        <v>7534760154</v>
       </c>
       <c r="C26" s="0">
-        <v>27195121652</v>
+        <v>8810428605</v>
       </c>
       <c r="D26" s="0">
-        <v>1909770</v>
+        <v>419345</v>
       </c>
       <c r="E26" s="0">
-        <v>291</v>
+        <v>179</v>
       </c>
       <c r="F26" s="0">
-        <v>22930</v>
+        <v>46204</v>
       </c>
       <c r="G26" s="0">
-        <v>1.6100000000000001</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H26" s="0">
-        <v>13.66</v>
+        <v>6.1600000000000001</v>
       </c>
       <c r="I26" s="0">
-        <v>84.439999999999998</v>
+        <v>85.519999999999996</v>
       </c>
       <c r="J26" s="0">
-        <v>4070</v>
+        <v>1067</v>
       </c>
       <c r="K26" s="0">
-        <v>7935.8400000000001</v>
+        <v>7552.21</v>
       </c>
       <c r="L26" s="0">
-        <v>27.239999999999998</v>
+        <v>42.259999999999998</v>
       </c>
       <c r="M26" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="27">
@@ -1282,37 +1306,37 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>6602447079</v>
+        <v>75592980893</v>
       </c>
       <c r="C27" s="0">
-        <v>7580779920</v>
+        <v>87148108858</v>
       </c>
       <c r="D27" s="0">
-        <v>2159766</v>
+        <v>879662</v>
       </c>
       <c r="E27" s="0">
-        <v>305</v>
+        <v>179</v>
       </c>
       <c r="F27" s="0">
-        <v>3919</v>
+        <v>375322</v>
       </c>
       <c r="G27" s="0">
-        <v>1.1200000000000001</v>
+        <v>3.79</v>
       </c>
       <c r="H27" s="0">
-        <v>13.869999999999999</v>
+        <v>12.300000000000001</v>
       </c>
       <c r="I27" s="0">
-        <v>87.090000000000003</v>
+        <v>86.739999999999995</v>
       </c>
       <c r="J27" s="0">
-        <v>6335</v>
+        <v>1297</v>
       </c>
       <c r="K27" s="0">
-        <v>7957.6999999999998</v>
+        <v>3642.5700000000002</v>
       </c>
       <c r="L27" s="0">
-        <v>26.059999999999999</v>
+        <v>20.34</v>
       </c>
       <c r="M27" s="0">
         <v>0.050999999999999997</v>
@@ -1323,40 +1347,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>12937852301</v>
+        <v>998927544</v>
       </c>
       <c r="C28" s="0">
-        <v>15888310841</v>
+        <v>1144280770</v>
       </c>
       <c r="D28" s="0">
-        <v>1421137</v>
+        <v>657633</v>
       </c>
       <c r="E28" s="0">
-        <v>223</v>
+        <v>179</v>
       </c>
       <c r="F28" s="0">
-        <v>15820</v>
+        <v>4913</v>
       </c>
       <c r="G28" s="0">
-        <v>1.4199999999999999</v>
+        <v>2.8199999999999998</v>
       </c>
       <c r="H28" s="0">
-        <v>12.83</v>
+        <v>9.1099999999999994</v>
       </c>
       <c r="I28" s="0">
-        <v>81.430000000000007</v>
+        <v>87.299999999999997</v>
       </c>
       <c r="J28" s="0">
-        <v>4506</v>
+        <v>1301</v>
       </c>
       <c r="K28" s="0">
-        <v>8030.8500000000004</v>
+        <v>3628.0999999999999</v>
       </c>
       <c r="L28" s="0">
-        <v>36.020000000000003</v>
+        <v>20.27</v>
       </c>
       <c r="M28" s="0">
-        <v>0.071999999999999995</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="29">
@@ -1364,40 +1388,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>22896809589</v>
+        <v>47537331635</v>
       </c>
       <c r="C29" s="0">
-        <v>28928489479</v>
+        <v>54552621363</v>
       </c>
       <c r="D29" s="0">
-        <v>1935016</v>
+        <v>798838</v>
       </c>
       <c r="E29" s="0">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="F29" s="0">
-        <v>18090</v>
+        <v>178101</v>
       </c>
       <c r="G29" s="0">
-        <v>1.21</v>
+        <v>2.6099999999999999</v>
       </c>
       <c r="H29" s="0">
-        <v>14.300000000000001</v>
+        <v>10.609999999999999</v>
       </c>
       <c r="I29" s="0">
-        <v>79.150000000000006</v>
+        <v>87.140000000000001</v>
       </c>
       <c r="J29" s="0">
-        <v>6056</v>
+        <v>1717</v>
       </c>
       <c r="K29" s="0">
-        <v>8626.0400000000009</v>
+        <v>5065.0500000000002</v>
       </c>
       <c r="L29" s="0">
-        <v>32.640000000000001</v>
+        <v>28.32</v>
       </c>
       <c r="M29" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="30">
@@ -1405,40 +1429,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>5663864</v>
+        <v>10877551232</v>
       </c>
       <c r="C30" s="0">
-        <v>7539144</v>
+        <v>12560820189</v>
       </c>
       <c r="D30" s="0">
-        <v>50261</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0">
-        <v>318</v>
+        <v>227</v>
       </c>
       <c r="F30" s="0">
-        <v>13</v>
+        <v>33688</v>
       </c>
       <c r="G30" s="0">
-        <v>0.089999999999999997</v>
+        <v>0</v>
       </c>
       <c r="H30" s="0">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="I30" s="0">
-        <v>75.129999999999995</v>
+        <v>86.599999999999994</v>
       </c>
       <c r="J30" s="0">
-        <v>1824</v>
+        <v>1638</v>
       </c>
       <c r="K30" s="0">
-        <v>5208.2700000000004</v>
+        <v>5416.7799999999997</v>
       </c>
       <c r="L30" s="0">
-        <v>16.379999999999999</v>
+        <v>23.800000000000001</v>
       </c>
       <c r="M30" s="0">
-        <v>0.037999999999999999</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1446,37 +1470,37 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>69993183659</v>
+        <v>41641443129</v>
       </c>
       <c r="C31" s="0">
-        <v>85137298994</v>
+        <v>50016551380</v>
       </c>
       <c r="D31" s="0">
-        <v>1716824</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="F31" s="0">
-        <v>67615</v>
+        <v>66588</v>
       </c>
       <c r="G31" s="0">
-        <v>1.3600000000000001</v>
+        <v>0</v>
       </c>
       <c r="H31" s="0">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="I31" s="0">
-        <v>82.209999999999994</v>
+        <v>83.260000000000005</v>
       </c>
       <c r="J31" s="0">
-        <v>4449</v>
+        <v>3482</v>
       </c>
       <c r="K31" s="0">
-        <v>9805.8099999999995</v>
+        <v>7027.1199999999999</v>
       </c>
       <c r="L31" s="0">
-        <v>34.579999999999998</v>
+        <v>32.57</v>
       </c>
       <c r="M31" s="0">
         <v>0.070000000000000007</v>
@@ -1487,40 +1511,40 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>22755391389</v>
+        <v>15988719928</v>
       </c>
       <c r="C32" s="0">
-        <v>28670796989</v>
+        <v>18980308189</v>
       </c>
       <c r="D32" s="0">
-        <v>2183610</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0">
-        <v>330</v>
+        <v>243</v>
       </c>
       <c r="F32" s="0">
-        <v>16082</v>
+        <v>21011</v>
       </c>
       <c r="G32" s="0">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="H32" s="0">
-        <v>13.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="I32" s="0">
-        <v>79.370000000000005</v>
+        <v>84.239999999999995</v>
       </c>
       <c r="J32" s="0">
-        <v>5355</v>
+        <v>3724</v>
       </c>
       <c r="K32" s="0">
-        <v>11037.6</v>
+        <v>7117.2700000000004</v>
       </c>
       <c r="L32" s="0">
-        <v>33.200000000000003</v>
+        <v>29.34</v>
       </c>
       <c r="M32" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="33">
@@ -1528,40 +1552,368 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>968994985638</v>
+        <v>23086790421</v>
       </c>
       <c r="C33" s="0">
-        <v>1156407845970</v>
+        <v>27863099120</v>
       </c>
       <c r="D33" s="0">
-        <v>0</v>
+        <v>1548810</v>
       </c>
       <c r="E33" s="0">
-        <v>132</v>
+        <v>260</v>
       </c>
       <c r="F33" s="0">
-        <v>7542544</v>
+        <v>31079</v>
       </c>
       <c r="G33" s="0">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="H33" s="0">
-        <v>0</v>
+        <v>12.789999999999999</v>
       </c>
       <c r="I33" s="0">
-        <v>83.790000000000006</v>
+        <v>82.859999999999999</v>
       </c>
       <c r="J33" s="0">
-        <v>946</v>
+        <v>3474</v>
       </c>
       <c r="K33" s="0">
-        <v>4051.6100000000001</v>
+        <v>8130.29</v>
       </c>
       <c r="L33" s="0">
-        <v>26.57</v>
+        <v>31.48</v>
       </c>
       <c r="M33" s="0">
         <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>22962219029</v>
+      </c>
+      <c r="C34" s="0">
+        <v>27195121652</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1909770</v>
+      </c>
+      <c r="E34" s="0">
+        <v>291</v>
+      </c>
+      <c r="F34" s="0">
+        <v>22930</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.6100000000000001</v>
+      </c>
+      <c r="H34" s="0">
+        <v>13.66</v>
+      </c>
+      <c r="I34" s="0">
+        <v>84.439999999999998</v>
+      </c>
+      <c r="J34" s="0">
+        <v>4070</v>
+      </c>
+      <c r="K34" s="0">
+        <v>7935.8400000000001</v>
+      </c>
+      <c r="L34" s="0">
+        <v>27.239999999999998</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.057000000000000002</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>6602447079</v>
+      </c>
+      <c r="C35" s="0">
+        <v>7580779920</v>
+      </c>
+      <c r="D35" s="0">
+        <v>2159766</v>
+      </c>
+      <c r="E35" s="0">
+        <v>305</v>
+      </c>
+      <c r="F35" s="0">
+        <v>3919</v>
+      </c>
+      <c r="G35" s="0">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H35" s="0">
+        <v>13.869999999999999</v>
+      </c>
+      <c r="I35" s="0">
+        <v>87.090000000000003</v>
+      </c>
+      <c r="J35" s="0">
+        <v>6335</v>
+      </c>
+      <c r="K35" s="0">
+        <v>7957.6999999999998</v>
+      </c>
+      <c r="L35" s="0">
+        <v>26.059999999999999</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.050999999999999997</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
+        <v>12937852301</v>
+      </c>
+      <c r="C36" s="0">
+        <v>15888310841</v>
+      </c>
+      <c r="D36" s="0">
+        <v>1421137</v>
+      </c>
+      <c r="E36" s="0">
+        <v>223</v>
+      </c>
+      <c r="F36" s="0">
+        <v>15820</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1.4199999999999999</v>
+      </c>
+      <c r="H36" s="0">
+        <v>12.83</v>
+      </c>
+      <c r="I36" s="0">
+        <v>81.430000000000007</v>
+      </c>
+      <c r="J36" s="0">
+        <v>4506</v>
+      </c>
+      <c r="K36" s="0">
+        <v>8030.8500000000004</v>
+      </c>
+      <c r="L36" s="0">
+        <v>36.020000000000003</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.071999999999999995</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
+        <v>22896809589</v>
+      </c>
+      <c r="C37" s="0">
+        <v>28928489479</v>
+      </c>
+      <c r="D37" s="0">
+        <v>1935016</v>
+      </c>
+      <c r="E37" s="0">
+        <v>265</v>
+      </c>
+      <c r="F37" s="0">
+        <v>18090</v>
+      </c>
+      <c r="G37" s="0">
+        <v>1.21</v>
+      </c>
+      <c r="H37" s="0">
+        <v>14.300000000000001</v>
+      </c>
+      <c r="I37" s="0">
+        <v>79.150000000000006</v>
+      </c>
+      <c r="J37" s="0">
+        <v>6056</v>
+      </c>
+      <c r="K37" s="0">
+        <v>8626.0400000000009</v>
+      </c>
+      <c r="L37" s="0">
+        <v>32.640000000000001</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0">
+        <v>5663864</v>
+      </c>
+      <c r="C38" s="0">
+        <v>7539144</v>
+      </c>
+      <c r="D38" s="0">
+        <v>50261</v>
+      </c>
+      <c r="E38" s="0">
+        <v>318</v>
+      </c>
+      <c r="F38" s="0">
+        <v>13</v>
+      </c>
+      <c r="G38" s="0">
+        <v>0.089999999999999997</v>
+      </c>
+      <c r="H38" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="I38" s="0">
+        <v>75.129999999999995</v>
+      </c>
+      <c r="J38" s="0">
+        <v>1824</v>
+      </c>
+      <c r="K38" s="0">
+        <v>5208.2700000000004</v>
+      </c>
+      <c r="L38" s="0">
+        <v>16.379999999999999</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0.037999999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0">
+        <v>69993183659</v>
+      </c>
+      <c r="C39" s="0">
+        <v>85137298994</v>
+      </c>
+      <c r="D39" s="0">
+        <v>1716824</v>
+      </c>
+      <c r="E39" s="0">
+        <v>290</v>
+      </c>
+      <c r="F39" s="0">
+        <v>67615</v>
+      </c>
+      <c r="G39" s="0">
+        <v>1.3600000000000001</v>
+      </c>
+      <c r="H39" s="0">
+        <v>12.25</v>
+      </c>
+      <c r="I39" s="0">
+        <v>82.209999999999994</v>
+      </c>
+      <c r="J39" s="0">
+        <v>4449</v>
+      </c>
+      <c r="K39" s="0">
+        <v>9805.8099999999995</v>
+      </c>
+      <c r="L39" s="0">
+        <v>34.579999999999998</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0.070000000000000007</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0">
+        <v>22755391389</v>
+      </c>
+      <c r="C40" s="0">
+        <v>28670796989</v>
+      </c>
+      <c r="D40" s="0">
+        <v>2183610</v>
+      </c>
+      <c r="E40" s="0">
+        <v>330</v>
+      </c>
+      <c r="F40" s="0">
+        <v>16082</v>
+      </c>
+      <c r="G40" s="0">
+        <v>1.22</v>
+      </c>
+      <c r="H40" s="0">
+        <v>13.050000000000001</v>
+      </c>
+      <c r="I40" s="0">
+        <v>79.370000000000005</v>
+      </c>
+      <c r="J40" s="0">
+        <v>5355</v>
+      </c>
+      <c r="K40" s="0">
+        <v>11037.6</v>
+      </c>
+      <c r="L40" s="0">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0.066000000000000003</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="0">
+        <v>996804453569</v>
+      </c>
+      <c r="C41" s="0">
+        <v>1189747344926</v>
+      </c>
+      <c r="D41" s="0">
+        <v>0</v>
+      </c>
+      <c r="E41" s="0">
+        <v>131</v>
+      </c>
+      <c r="F41" s="0">
+        <v>8067995</v>
+      </c>
+      <c r="G41" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" s="0">
+        <v>0</v>
+      </c>
+      <c r="I41" s="0">
+        <v>83.780000000000001</v>
+      </c>
+      <c r="J41" s="0">
+        <v>916</v>
+      </c>
+      <c r="K41" s="0">
+        <v>4031.71</v>
+      </c>
+      <c r="L41" s="0">
+        <v>26.640000000000001</v>
+      </c>
+      <c r="M41" s="0">
+        <v>0.068000000000000005</v>
       </c>
     </row>
   </sheetData>
